--- a/data/processed/modeling/datos_ml_0.xlsx
+++ b/data/processed/modeling/datos_ml_0.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ML_Ready_Train'!$A$1:$CT$74</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ML_Ready_AllWeeks'!$A$1:$CT$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ML_Ready_Train'!$A$1:$CT$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ML_Ready_AllWeeks'!$A$1:$CT$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'README'!$A$1:$B$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -29,16 +29,13 @@
     <numFmt numFmtId="167" formatCode="0.000"/>
     <numFmt numFmtId="168" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -58,7 +55,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -66,21 +63,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -451,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT74"/>
+  <dimension ref="A1:CT82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -490,7 +479,7 @@
     <col width="23" customWidth="1" min="34" max="34"/>
     <col width="24" customWidth="1" min="35" max="35"/>
     <col width="29" customWidth="1" min="36" max="36"/>
-    <col width="21" customWidth="1" min="37" max="37"/>
+    <col width="22" customWidth="1" min="37" max="37"/>
     <col width="23" customWidth="1" min="38" max="38"/>
     <col width="18" customWidth="1" min="39" max="39"/>
     <col width="18" customWidth="1" min="40" max="40"/>
@@ -22696,8 +22685,2344 @@
         <v>-3.9255</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2026-W11</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D75" t="n">
+        <v>11</v>
+      </c>
+      <c r="E75" t="n">
+        <v>202611</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>59.96416353031891</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>53.96034228489324</v>
+      </c>
+      <c r="H75" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr"/>
+      <c r="K75" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1</v>
+      </c>
+      <c r="M75" s="4" t="inlineStr"/>
+      <c r="N75" s="4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" s="4" t="inlineStr"/>
+      <c r="Q75" s="4" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T75" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="W75" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="Z75" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AC75" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="6" t="n">
+        <v>0.5072463768115942</v>
+      </c>
+      <c r="AH75" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI75" s="6" t="n">
+        <v>-0.2289023717595146</v>
+      </c>
+      <c r="AJ75" s="6" t="n">
+        <v>0.02716856483114054</v>
+      </c>
+      <c r="AK75" s="6" t="n">
+        <v>0.1528107680126682</v>
+      </c>
+      <c r="AL75" s="6" t="n">
+        <v>0.0899896664219044</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>0.5391</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>-1.5346</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>-1.2892</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>0.8659</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>-0.3516</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>5.1237</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>-0.1761</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>5.1184</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>0.1208</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>-1.9431</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>0.9129</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>-4.172</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>-4.0996</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>1.8234</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>-4.3034</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>-4.1048</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>4.0212</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>-2.7523</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>3.3922</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>3.8642</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>-1.3758</v>
+      </c>
+      <c r="BJ75" t="n">
+        <v>3.6968</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>2.2819</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>-1.6165</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>1.4839</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>-4.0636</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>-4.0035</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>-1.2187</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>-1.059</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>0.7219</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>-0.2421</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>0.5526</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>4.9474</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>-0.1245</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>4.9431</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>-1.6287</v>
+      </c>
+      <c r="CB75" t="n">
+        <v>-1.6068</v>
+      </c>
+      <c r="CC75" t="n">
+        <v>0.6823</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>-3.6977</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>-3.6288</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="CG75" t="n">
+        <v>-3.9186</v>
+      </c>
+      <c r="CH75" t="n">
+        <v>-3.797</v>
+      </c>
+      <c r="CI75" t="n">
+        <v>3.4587</v>
+      </c>
+      <c r="CJ75" t="n">
+        <v>-2.368</v>
+      </c>
+      <c r="CK75" t="n">
+        <v>2.7723</v>
+      </c>
+      <c r="CL75" t="n">
+        <v>3.5673</v>
+      </c>
+      <c r="CM75" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="CN75" t="n">
+        <v>3.406</v>
+      </c>
+      <c r="CO75" t="n">
+        <v>1.4292</v>
+      </c>
+      <c r="CP75" t="n">
+        <v>-1.5561</v>
+      </c>
+      <c r="CQ75" t="n">
+        <v>-0.319</v>
+      </c>
+      <c r="CR75" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="CS75" t="n">
+        <v>-3.504</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>-3.459</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2026-W12</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D76" t="n">
+        <v>12</v>
+      </c>
+      <c r="E76" t="n">
+        <v>202612</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="H76" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr"/>
+      <c r="K76" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L76" t="n">
+        <v>1</v>
+      </c>
+      <c r="M76" s="4" t="inlineStr"/>
+      <c r="N76" s="4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O76" t="n">
+        <v>1</v>
+      </c>
+      <c r="P76" s="4" t="inlineStr"/>
+      <c r="Q76" s="4" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R76" t="n">
+        <v>1</v>
+      </c>
+      <c r="S76" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T76" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
+      </c>
+      <c r="V76" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="W76" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="X76" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="Z76" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="AA76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB76" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AC76" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AD76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF76" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="AH76" s="6" t="n">
+        <v>0.09677419354838709</v>
+      </c>
+      <c r="AI76" s="6" t="n">
+        <v>-0.122060470324748</v>
+      </c>
+      <c r="AJ76" s="6" t="n">
+        <v>0.1211586643975283</v>
+      </c>
+      <c r="AK76" s="6" t="n">
+        <v>0.1413802016024813</v>
+      </c>
+      <c r="AL76" s="6" t="n">
+        <v>0.1312694330000048</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>-2.7467</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>-2.7071</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>1.4729</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>-0.4656</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>1.2599</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>4.4786</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>-0.0276</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>4.4773</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>0.1094</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>-1.8612</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>-1.8296</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>0.8066</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>-3.6312</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>-3.5412</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>1.6473</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>-3.4769</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>-3.1702</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>3.4595</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>-2.1054</v>
+      </c>
+      <c r="BG76" t="n">
+        <v>2.9444</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>5.7787</v>
+      </c>
+      <c r="BI76" t="n">
+        <v>-0.8456</v>
+      </c>
+      <c r="BJ76" t="n">
+        <v>5.7576</v>
+      </c>
+      <c r="BK76" t="n">
+        <v>3.4617</v>
+      </c>
+      <c r="BL76" t="n">
+        <v>-2.3829</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>2.7659</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>-2.6556</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>-2.5873</v>
+      </c>
+      <c r="BQ76" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="BR76" t="n">
+        <v>-2.2037</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>-2.1695</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>1.2319</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>-0.3652</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>1.0431</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>4.2603</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>4.2595</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>0.1221</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>-1.5255</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>-1.4806</v>
+      </c>
+      <c r="CC76" t="n">
+        <v>0.5057</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>-3.2505</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>-3.1854</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>1.2144</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>-3.0737</v>
+      </c>
+      <c r="CH76" t="n">
+        <v>-2.8276</v>
+      </c>
+      <c r="CI76" t="n">
+        <v>2.9284</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>-1.8726</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>2.3077</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>5.3765</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>-0.6819</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>5.3554</v>
+      </c>
+      <c r="CO76" t="n">
+        <v>2.568</v>
+      </c>
+      <c r="CP76" t="n">
+        <v>-2.0174</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>1.5268</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>0.2192</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>-2.1385</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>-2.0837</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2026-W13</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D77" t="n">
+        <v>13</v>
+      </c>
+      <c r="E77" t="n">
+        <v>202613</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr"/>
+      <c r="K77" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L77" t="n">
+        <v>1</v>
+      </c>
+      <c r="M77" s="4" t="inlineStr"/>
+      <c r="N77" s="4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O77" t="n">
+        <v>1</v>
+      </c>
+      <c r="P77" s="4" t="inlineStr"/>
+      <c r="Q77" s="4" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R77" t="n">
+        <v>1</v>
+      </c>
+      <c r="S77" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T77" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="W77" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="X77" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="Z77" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="AA77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB77" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AC77" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AD77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="6" t="n">
+        <v>0.7281553398058253</v>
+      </c>
+      <c r="AH77" s="6" t="n">
+        <v>0.4188034188034188</v>
+      </c>
+      <c r="AI77" s="6" t="n">
+        <v>-0.4370477568740955</v>
+      </c>
+      <c r="AJ77" s="6" t="n">
+        <v>-0.005462221777095377</v>
+      </c>
+      <c r="AK77" s="6" t="n">
+        <v>0.07403651115618662</v>
+      </c>
+      <c r="AL77" s="6" t="n">
+        <v>0.03428714468954562</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>0.9449</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>-2.6028</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>-2.3645</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>1.7853</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>-1.0946</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>1.2088</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>4.8797</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>4.8797</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>0.1785</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>-3.0794</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>-3.0567</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>-4.0889</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>-4.0336</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>1.8421</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>-3.9955</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>-3.7403</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>2.2923</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>-2.7722</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>-1.5526</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>4.3873</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>-1.3651</v>
+      </c>
+      <c r="BJ77" t="n">
+        <v>4.2743</v>
+      </c>
+      <c r="BK77" t="n">
+        <v>3.1379</v>
+      </c>
+      <c r="BL77" t="n">
+        <v>-2.122</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>2.4462</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>0.9036999999999999</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>-3.3832</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>-3.2575</v>
+      </c>
+      <c r="BQ77" t="n">
+        <v>0.5467</v>
+      </c>
+      <c r="BR77" t="n">
+        <v>-2.1471</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>-1.9887</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>1.5722</v>
+      </c>
+      <c r="BU77" t="n">
+        <v>-0.9373</v>
+      </c>
+      <c r="BV77" t="n">
+        <v>1.0417</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>4.6839</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY77" t="n">
+        <v>4.6839</v>
+      </c>
+      <c r="BZ77" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="CA77" t="n">
+        <v>-2.6109</v>
+      </c>
+      <c r="CB77" t="n">
+        <v>-2.5842</v>
+      </c>
+      <c r="CC77" t="n">
+        <v>0.5379</v>
+      </c>
+      <c r="CD77" t="n">
+        <v>-3.6053</v>
+      </c>
+      <c r="CE77" t="n">
+        <v>-3.5507</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>1.2956</v>
+      </c>
+      <c r="CG77" t="n">
+        <v>-3.597</v>
+      </c>
+      <c r="CH77" t="n">
+        <v>-3.4122</v>
+      </c>
+      <c r="CI77" t="n">
+        <v>1.6639</v>
+      </c>
+      <c r="CJ77" t="n">
+        <v>-2.4506</v>
+      </c>
+      <c r="CK77" t="n">
+        <v>-1.7214</v>
+      </c>
+      <c r="CL77" t="n">
+        <v>4.0783</v>
+      </c>
+      <c r="CM77" t="n">
+        <v>-1.0841</v>
+      </c>
+      <c r="CN77" t="n">
+        <v>3.9793</v>
+      </c>
+      <c r="CO77" t="n">
+        <v>2.2388</v>
+      </c>
+      <c r="CP77" t="n">
+        <v>-1.9702</v>
+      </c>
+      <c r="CQ77" t="n">
+        <v>0.8495</v>
+      </c>
+      <c r="CR77" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="CS77" t="n">
+        <v>-2.9943</v>
+      </c>
+      <c r="CT77" t="n">
+        <v>-2.9052</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2026-W14</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D78" t="n">
+        <v>14</v>
+      </c>
+      <c r="E78" t="n">
+        <v>202614</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="H78" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" t="n">
+        <v>1</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr"/>
+      <c r="K78" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" s="4" t="inlineStr"/>
+      <c r="N78" s="4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O78" t="n">
+        <v>1</v>
+      </c>
+      <c r="P78" s="4" t="inlineStr"/>
+      <c r="Q78" s="4" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R78" t="n">
+        <v>1</v>
+      </c>
+      <c r="S78" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T78" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="W78" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="X78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="Z78" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="AA78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB78" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AC78" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AD78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG78" s="6" t="n">
+        <v>0.6859504132231405</v>
+      </c>
+      <c r="AH78" s="6" t="n">
+        <v>0.286624203821656</v>
+      </c>
+      <c r="AI78" s="6" t="n">
+        <v>-0.262483994878361</v>
+      </c>
+      <c r="AJ78" s="6" t="n">
+        <v>0.06691471004989276</v>
+      </c>
+      <c r="AK78" s="6" t="n">
+        <v>0.1218498311249675</v>
+      </c>
+      <c r="AL78" s="6" t="n">
+        <v>0.09438227058743015</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>-1.1166</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>-1.0856</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>0.9129</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>-0.673</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>4.2252</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>4.2252</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>0.2139</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>-1.4711</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>-1.3855</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>1.4385</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>-3.6612</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>-3.4517</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>1.5104</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>-3.5504</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>-3.3027</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>2.0997</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>-1.8477</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>0.7544</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>3.6005</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>-1.1864</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>3.4402</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>3.0526</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>-1.6657</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>2.6146</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>-3.4428</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>-3.4088</v>
+      </c>
+      <c r="BQ78" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="BR78" t="n">
+        <v>-0.7923</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>-0.755</v>
+      </c>
+      <c r="BT78" t="n">
+        <v>0.7932</v>
+      </c>
+      <c r="BU78" t="n">
+        <v>-0.1965</v>
+      </c>
+      <c r="BV78" t="n">
+        <v>0.6663</v>
+      </c>
+      <c r="BW78" t="n">
+        <v>4.0466</v>
+      </c>
+      <c r="BX78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY78" t="n">
+        <v>4.0466</v>
+      </c>
+      <c r="BZ78" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="CA78" t="n">
+        <v>-1.2722</v>
+      </c>
+      <c r="CB78" t="n">
+        <v>-1.1729</v>
+      </c>
+      <c r="CC78" t="n">
+        <v>1.0843</v>
+      </c>
+      <c r="CD78" t="n">
+        <v>-3.3314</v>
+      </c>
+      <c r="CE78" t="n">
+        <v>-3.1612</v>
+      </c>
+      <c r="CF78" t="n">
+        <v>1.0759</v>
+      </c>
+      <c r="CG78" t="n">
+        <v>-3.2138</v>
+      </c>
+      <c r="CH78" t="n">
+        <v>-3.0303</v>
+      </c>
+      <c r="CI78" t="n">
+        <v>1.1975</v>
+      </c>
+      <c r="CJ78" t="n">
+        <v>-1.6219</v>
+      </c>
+      <c r="CK78" t="n">
+        <v>-0.8354</v>
+      </c>
+      <c r="CL78" t="n">
+        <v>3.2917</v>
+      </c>
+      <c r="CM78" t="n">
+        <v>-0.9075</v>
+      </c>
+      <c r="CN78" t="n">
+        <v>3.1565</v>
+      </c>
+      <c r="CO78" t="n">
+        <v>2.2194</v>
+      </c>
+      <c r="CP78" t="n">
+        <v>-1.5656</v>
+      </c>
+      <c r="CQ78" t="n">
+        <v>1.4312</v>
+      </c>
+      <c r="CR78" t="n">
+        <v>0.1698</v>
+      </c>
+      <c r="CS78" t="n">
+        <v>-2.9059</v>
+      </c>
+      <c r="CT78" t="n">
+        <v>-2.8817</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D79" t="n">
+        <v>15</v>
+      </c>
+      <c r="E79" t="n">
+        <v>202615</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr"/>
+      <c r="K79" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="4" t="inlineStr"/>
+      <c r="N79" s="4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" s="4" t="inlineStr"/>
+      <c r="Q79" s="4" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T79" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="W79" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="Z79" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AC79" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="6" t="n">
+        <v>0.7864077669902912</v>
+      </c>
+      <c r="AH79" s="6" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="AI79" s="6" t="n">
+        <v>-0.2191235059760956</v>
+      </c>
+      <c r="AJ79" s="6" t="n">
+        <v>0.110472470964671</v>
+      </c>
+      <c r="AK79" s="6" t="n">
+        <v>0.1378848728246319</v>
+      </c>
+      <c r="AL79" s="6" t="n">
+        <v>0.1241786718946514</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>-2.9573</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>-2.905</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>2.6321</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>-0.7219</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>2.4725</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>3.788</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>3.788</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>-2.5166</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>-2.5102</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>1.3749</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>-3.1085</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>-2.8138</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>1.1887</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>-3.0673</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>-2.8283</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>2.1344</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>-2.274</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>-0.5322</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>4.7339</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>-1.3501</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>4.6474</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>2.7632</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>-2.0223</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>1.8978</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>1.8877</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>-3.3528</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>-2.9099</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>-2.4101</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>-2.3642</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>2.2569</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>-0.5517</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>3.6073</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>3.6073</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>-2.0647</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>-2.0389</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>1.0379</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>-2.7146</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>-2.4623</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0.7416</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>-2.7015</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>-2.5442</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1.6183</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>-2.0861</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>-1.1216</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>4.3819</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>4.2718</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>1.9213</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>-1.7273</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>0.5622</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>1.4867</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>-2.9556</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>-2.5742</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D80" t="n">
+        <v>16</v>
+      </c>
+      <c r="E80" t="n">
+        <v>202616</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr"/>
+      <c r="K80" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" s="4" t="inlineStr"/>
+      <c r="N80" s="4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" s="4" t="inlineStr"/>
+      <c r="Q80" s="4" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T80" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="W80" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="Z80" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AC80" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="6" t="n">
+        <v>0.6880733944954128</v>
+      </c>
+      <c r="AH80" s="6" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="AI80" s="6" t="n">
+        <v>-0.2512820512820513</v>
+      </c>
+      <c r="AJ80" s="6" t="n">
+        <v>0.06687791935569266</v>
+      </c>
+      <c r="AK80" s="6" t="n">
+        <v>0.07456</v>
+      </c>
+      <c r="AL80" s="6" t="n">
+        <v>0.07071895967784633</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>0.1836</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>-1.643</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>-1.5789</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>1.0221</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>-0.5624</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>0.6362</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>3.5082</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>3.5082</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0.2708</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>-2.0426</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>-1.9685</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>0.9311</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>-4.1604</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>-4.0853</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>-3.9013</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>-2.769</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>2.6725</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>-3.173</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>-1.8654</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>4.3789</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>-1.4892</v>
+      </c>
+      <c r="BJ80" t="n">
+        <v>4.2478</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>1.6866</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>-2.2104</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>-1.2685</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>0.5974</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>-2.9463</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>-2.8469</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>-1.2769</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>0.9207</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>-0.4438</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>0.6162</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>3.2982</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>3.2982</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>-1.7085</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>-1.6505</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0.6621</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>-3.7621</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>-3.6988</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>2.2297</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>-3.5366</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>-2.9844</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>2.056</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>-2.8608</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>-2.0378</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>4.0346</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>-1.1268</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>3.9264</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>1.0546</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>-2.0296</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>-1.5878</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>-2.5093</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D81" t="n">
+        <v>17</v>
+      </c>
+      <c r="E81" t="n">
+        <v>202617</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr"/>
+      <c r="K81" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="4" t="inlineStr"/>
+      <c r="N81" s="4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" s="4" t="inlineStr"/>
+      <c r="Q81" s="4" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
+      <c r="S81" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T81" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="W81" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AC81" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="6" t="n">
+        <v>0.6883116883116883</v>
+      </c>
+      <c r="AH81" s="6" t="n">
+        <v>0.04035874439461883</v>
+      </c>
+      <c r="AI81" s="6" t="n">
+        <v>-0.2435703479576399</v>
+      </c>
+      <c r="AJ81" s="6" t="n">
+        <v>0.04214202741675304</v>
+      </c>
+      <c r="AK81" s="6" t="n">
+        <v>0.009624958513109858</v>
+      </c>
+      <c r="AL81" s="6" t="n">
+        <v>0.02588349296493145</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>-2.2735</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>-2.1914</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>1.0951</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>-0.5065</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>0.7788</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>3.6985</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>-0.0638</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>3.6934</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>-1.559</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>-1.5138</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>0.6987</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>-4.2835</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>-4.2366</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>1.5467</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>-4.1642</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>-4.0006</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>2.8576</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>-3.3365</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>-1.9461</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>3.8601</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>-1.6214</v>
+      </c>
+      <c r="BJ81" t="n">
+        <v>3.6375</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>1.3895</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>-1.6831</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>-0.6701</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>-3.1317</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>-3.0611</v>
+      </c>
+      <c r="BQ81" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="BR81" t="n">
+        <v>-1.7612</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>-1.6866</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>1.0431</v>
+      </c>
+      <c r="BU81" t="n">
+        <v>-0.3913</v>
+      </c>
+      <c r="BV81" t="n">
+        <v>0.8066</v>
+      </c>
+      <c r="BW81" t="n">
+        <v>3.5401</v>
+      </c>
+      <c r="BX81" t="n">
+        <v>-0.0446</v>
+      </c>
+      <c r="BY81" t="n">
+        <v>3.5362</v>
+      </c>
+      <c r="BZ81" t="n">
+        <v>0.1184</v>
+      </c>
+      <c r="CA81" t="n">
+        <v>-1.2502</v>
+      </c>
+      <c r="CB81" t="n">
+        <v>-1.1974</v>
+      </c>
+      <c r="CC81" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="CD81" t="n">
+        <v>-3.8559</v>
+      </c>
+      <c r="CE81" t="n">
+        <v>-3.8127</v>
+      </c>
+      <c r="CF81" t="n">
+        <v>1.0664</v>
+      </c>
+      <c r="CG81" t="n">
+        <v>-3.8059</v>
+      </c>
+      <c r="CH81" t="n">
+        <v>-3.6884</v>
+      </c>
+      <c r="CI81" t="n">
+        <v>2.334</v>
+      </c>
+      <c r="CJ81" t="n">
+        <v>-3.017</v>
+      </c>
+      <c r="CK81" t="n">
+        <v>-2.0189</v>
+      </c>
+      <c r="CL81" t="n">
+        <v>3.5236</v>
+      </c>
+      <c r="CM81" t="n">
+        <v>-1.4236</v>
+      </c>
+      <c r="CN81" t="n">
+        <v>3.2954</v>
+      </c>
+      <c r="CO81" t="n">
+        <v>0.8035</v>
+      </c>
+      <c r="CP81" t="n">
+        <v>-1.4988</v>
+      </c>
+      <c r="CQ81" t="n">
+        <v>-1.0571</v>
+      </c>
+      <c r="CR81" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="CS81" t="n">
+        <v>-2.7813</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>-2.7605</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D82" t="n">
+        <v>18</v>
+      </c>
+      <c r="E82" t="n">
+        <v>202618</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr"/>
+      <c r="K82" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="4" t="inlineStr"/>
+      <c r="N82" s="4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
+      <c r="P82" s="4" t="inlineStr"/>
+      <c r="Q82" s="4" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T82" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="W82" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="Z82" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AC82" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="6" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AH82" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI82" s="6" t="n">
+        <v>-0.1587301587301587</v>
+      </c>
+      <c r="AJ82" s="6" t="n">
+        <v>0.0732244276596991</v>
+      </c>
+      <c r="AK82" s="6" t="n">
+        <v>0.1154303847679492</v>
+      </c>
+      <c r="AL82" s="6" t="n">
+        <v>0.09432740621382416</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>-1.2732</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>-1.2498</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>1.9865</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>-0.369</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>1.8763</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>3.0365</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>-0.2399</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>3.0043</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>-2.0539</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>-2.0407</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>1.1117</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>-4.0548</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>-3.9503</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>1.6203</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>-3.8672</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>-3.646</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>2.6413</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>-3.7155</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>-2.9814</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>3.7522</v>
+      </c>
+      <c r="BI82" t="n">
+        <v>-1.6236</v>
+      </c>
+      <c r="BJ82" t="n">
+        <v>3.5101</v>
+      </c>
+      <c r="BK82" t="n">
+        <v>1.4559</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>-1.6614</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>-0.506</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>-2.6749</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>-2.636</v>
+      </c>
+      <c r="BQ82" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="BR82" t="n">
+        <v>-0.9604</v>
+      </c>
+      <c r="BS82" t="n">
+        <v>-0.9393</v>
+      </c>
+      <c r="BT82" t="n">
+        <v>1.8382</v>
+      </c>
+      <c r="BU82" t="n">
+        <v>-0.3019</v>
+      </c>
+      <c r="BV82" t="n">
+        <v>1.7411</v>
+      </c>
+      <c r="BW82" t="n">
+        <v>2.8293</v>
+      </c>
+      <c r="BX82" t="n">
+        <v>-0.2311</v>
+      </c>
+      <c r="BY82" t="n">
+        <v>2.7936</v>
+      </c>
+      <c r="BZ82" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="CA82" t="n">
+        <v>-1.7219</v>
+      </c>
+      <c r="CB82" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="CC82" t="n">
+        <v>0.9461000000000001</v>
+      </c>
+      <c r="CD82" t="n">
+        <v>-3.6083</v>
+      </c>
+      <c r="CE82" t="n">
+        <v>-3.4942</v>
+      </c>
+      <c r="CF82" t="n">
+        <v>1.0596</v>
+      </c>
+      <c r="CG82" t="n">
+        <v>-3.4815</v>
+      </c>
+      <c r="CH82" t="n">
+        <v>-3.3342</v>
+      </c>
+      <c r="CI82" t="n">
+        <v>2.0325</v>
+      </c>
+      <c r="CJ82" t="n">
+        <v>-3.4029</v>
+      </c>
+      <c r="CK82" t="n">
+        <v>-2.9042</v>
+      </c>
+      <c r="CL82" t="n">
+        <v>3.427</v>
+      </c>
+      <c r="CM82" t="n">
+        <v>-1.3787</v>
+      </c>
+      <c r="CN82" t="n">
+        <v>3.1946</v>
+      </c>
+      <c r="CO82" t="n">
+        <v>0.9693000000000001</v>
+      </c>
+      <c r="CP82" t="n">
+        <v>-1.4281</v>
+      </c>
+      <c r="CQ82" t="n">
+        <v>-0.7934</v>
+      </c>
+      <c r="CR82" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="CS82" t="n">
+        <v>-2.3866</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>-2.3679</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CT74"/>
+  <autoFilter ref="A1:CT82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22708,7 +25033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CT78"/>
+  <dimension ref="A1:CT82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -22747,7 +25072,7 @@
     <col width="23" customWidth="1" min="34" max="34"/>
     <col width="24" customWidth="1" min="35" max="35"/>
     <col width="29" customWidth="1" min="36" max="36"/>
-    <col width="21" customWidth="1" min="37" max="37"/>
+    <col width="22" customWidth="1" min="37" max="37"/>
     <col width="23" customWidth="1" min="38" max="38"/>
     <col width="18" customWidth="1" min="39" max="39"/>
     <col width="18" customWidth="1" min="40" max="40"/>
@@ -45041,13 +47366,13 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF75" t="n">
         <v>0</v>
       </c>
       <c r="AG75" s="6" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.5072463768115942</v>
       </c>
       <c r="AH75" s="6" t="n">
         <v>0.2</v>
@@ -45056,74 +47381,194 @@
         <v>-0.2289023717595146</v>
       </c>
       <c r="AJ75" s="6" t="n">
-        <v>0.1009353369037931</v>
+        <v>0.02716856483114054</v>
       </c>
       <c r="AK75" s="6" t="n">
         <v>0.1528107680126682</v>
       </c>
       <c r="AL75" s="6" t="n">
-        <v>0.1268730524582307</v>
-      </c>
-      <c r="AM75" t="inlineStr"/>
-      <c r="AN75" t="inlineStr"/>
-      <c r="AO75" t="inlineStr"/>
-      <c r="AP75" t="inlineStr"/>
-      <c r="AQ75" t="inlineStr"/>
-      <c r="AR75" t="inlineStr"/>
-      <c r="AS75" t="inlineStr"/>
-      <c r="AT75" t="inlineStr"/>
-      <c r="AU75" t="inlineStr"/>
-      <c r="AV75" t="inlineStr"/>
-      <c r="AW75" t="inlineStr"/>
-      <c r="AX75" t="inlineStr"/>
-      <c r="AY75" t="inlineStr"/>
-      <c r="AZ75" t="inlineStr"/>
-      <c r="BA75" t="inlineStr"/>
-      <c r="BB75" t="inlineStr"/>
-      <c r="BC75" t="inlineStr"/>
-      <c r="BD75" t="inlineStr"/>
-      <c r="BE75" t="inlineStr"/>
-      <c r="BF75" t="inlineStr"/>
-      <c r="BG75" t="inlineStr"/>
-      <c r="BH75" t="inlineStr"/>
-      <c r="BI75" t="inlineStr"/>
-      <c r="BJ75" t="inlineStr"/>
-      <c r="BK75" t="inlineStr"/>
-      <c r="BL75" t="inlineStr"/>
-      <c r="BM75" t="inlineStr"/>
-      <c r="BN75" t="inlineStr"/>
-      <c r="BO75" t="inlineStr"/>
-      <c r="BP75" t="inlineStr"/>
-      <c r="BQ75" t="inlineStr"/>
-      <c r="BR75" t="inlineStr"/>
-      <c r="BS75" t="inlineStr"/>
-      <c r="BT75" t="inlineStr"/>
-      <c r="BU75" t="inlineStr"/>
-      <c r="BV75" t="inlineStr"/>
-      <c r="BW75" t="inlineStr"/>
-      <c r="BX75" t="inlineStr"/>
-      <c r="BY75" t="inlineStr"/>
-      <c r="BZ75" t="inlineStr"/>
-      <c r="CA75" t="inlineStr"/>
-      <c r="CB75" t="inlineStr"/>
-      <c r="CC75" t="inlineStr"/>
-      <c r="CD75" t="inlineStr"/>
-      <c r="CE75" t="inlineStr"/>
-      <c r="CF75" t="inlineStr"/>
-      <c r="CG75" t="inlineStr"/>
-      <c r="CH75" t="inlineStr"/>
-      <c r="CI75" t="inlineStr"/>
-      <c r="CJ75" t="inlineStr"/>
-      <c r="CK75" t="inlineStr"/>
-      <c r="CL75" t="inlineStr"/>
-      <c r="CM75" t="inlineStr"/>
-      <c r="CN75" t="inlineStr"/>
-      <c r="CO75" t="inlineStr"/>
-      <c r="CP75" t="inlineStr"/>
-      <c r="CQ75" t="inlineStr"/>
-      <c r="CR75" t="inlineStr"/>
-      <c r="CS75" t="inlineStr"/>
-      <c r="CT75" t="inlineStr"/>
+        <v>0.0899896664219044</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>0.5391</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>-1.5346</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>-1.2892</v>
+      </c>
+      <c r="AP75" t="n">
+        <v>0.8659</v>
+      </c>
+      <c r="AQ75" t="n">
+        <v>-0.3516</v>
+      </c>
+      <c r="AR75" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="AS75" t="n">
+        <v>5.1237</v>
+      </c>
+      <c r="AT75" t="n">
+        <v>-0.1761</v>
+      </c>
+      <c r="AU75" t="n">
+        <v>5.1184</v>
+      </c>
+      <c r="AV75" t="n">
+        <v>0.1208</v>
+      </c>
+      <c r="AW75" t="n">
+        <v>-1.9431</v>
+      </c>
+      <c r="AX75" t="n">
+        <v>-1.91</v>
+      </c>
+      <c r="AY75" t="n">
+        <v>0.9129</v>
+      </c>
+      <c r="AZ75" t="n">
+        <v>-4.172</v>
+      </c>
+      <c r="BA75" t="n">
+        <v>-4.0996</v>
+      </c>
+      <c r="BB75" t="n">
+        <v>1.8234</v>
+      </c>
+      <c r="BC75" t="n">
+        <v>-4.3034</v>
+      </c>
+      <c r="BD75" t="n">
+        <v>-4.1048</v>
+      </c>
+      <c r="BE75" t="n">
+        <v>4.0212</v>
+      </c>
+      <c r="BF75" t="n">
+        <v>-2.7523</v>
+      </c>
+      <c r="BG75" t="n">
+        <v>3.3922</v>
+      </c>
+      <c r="BH75" t="n">
+        <v>3.8642</v>
+      </c>
+      <c r="BI75" t="n">
+        <v>-1.3758</v>
+      </c>
+      <c r="BJ75" t="n">
+        <v>3.6968</v>
+      </c>
+      <c r="BK75" t="n">
+        <v>2.2819</v>
+      </c>
+      <c r="BL75" t="n">
+        <v>-1.6165</v>
+      </c>
+      <c r="BM75" t="n">
+        <v>1.4839</v>
+      </c>
+      <c r="BN75" t="n">
+        <v>0.7501</v>
+      </c>
+      <c r="BO75" t="n">
+        <v>-4.0636</v>
+      </c>
+      <c r="BP75" t="n">
+        <v>-4.0035</v>
+      </c>
+      <c r="BQ75" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BR75" t="n">
+        <v>-1.2187</v>
+      </c>
+      <c r="BS75" t="n">
+        <v>-1.059</v>
+      </c>
+      <c r="BT75" t="n">
+        <v>0.7219</v>
+      </c>
+      <c r="BU75" t="n">
+        <v>-0.2421</v>
+      </c>
+      <c r="BV75" t="n">
+        <v>0.5526</v>
+      </c>
+      <c r="BW75" t="n">
+        <v>4.9474</v>
+      </c>
+      <c r="BX75" t="n">
+        <v>-0.1245</v>
+      </c>
+      <c r="BY75" t="n">
+        <v>4.9431</v>
+      </c>
+      <c r="BZ75" t="n">
+        <v>0.06560000000000001</v>
+      </c>
+      <c r="CA75" t="n">
+        <v>-1.6287</v>
+      </c>
+      <c r="CB75" t="n">
+        <v>-1.6068</v>
+      </c>
+      <c r="CC75" t="n">
+        <v>0.6823</v>
+      </c>
+      <c r="CD75" t="n">
+        <v>-3.6977</v>
+      </c>
+      <c r="CE75" t="n">
+        <v>-3.6288</v>
+      </c>
+      <c r="CF75" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="CG75" t="n">
+        <v>-3.9186</v>
+      </c>
+      <c r="CH75" t="n">
+        <v>-3.797</v>
+      </c>
+      <c r="CI75" t="n">
+        <v>3.4587</v>
+      </c>
+      <c r="CJ75" t="n">
+        <v>-2.368</v>
+      </c>
+      <c r="CK75" t="n">
+        <v>2.7723</v>
+      </c>
+      <c r="CL75" t="n">
+        <v>3.5673</v>
+      </c>
+      <c r="CM75" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="CN75" t="n">
+        <v>3.406</v>
+      </c>
+      <c r="CO75" t="n">
+        <v>1.4292</v>
+      </c>
+      <c r="CP75" t="n">
+        <v>-1.5561</v>
+      </c>
+      <c r="CQ75" t="n">
+        <v>-0.319</v>
+      </c>
+      <c r="CR75" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="CS75" t="n">
+        <v>-3.504</v>
+      </c>
+      <c r="CT75" t="n">
+        <v>-3.459</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
@@ -45213,13 +47658,13 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF76" t="n">
         <v>0</v>
       </c>
       <c r="AG76" s="6" t="n">
-        <v>0.6231884057971014</v>
+        <v>0.6842105263157895</v>
       </c>
       <c r="AH76" s="6" t="n">
         <v>0.09677419354838709</v>
@@ -45228,74 +47673,194 @@
         <v>-0.122060470324748</v>
       </c>
       <c r="AJ76" s="6" t="n">
-        <v>0.1052090920574953</v>
+        <v>0.1211586643975283</v>
       </c>
       <c r="AK76" s="6" t="n">
         <v>0.1413802016024813</v>
       </c>
       <c r="AL76" s="6" t="n">
-        <v>0.1232946468299883</v>
-      </c>
-      <c r="AM76" t="inlineStr"/>
-      <c r="AN76" t="inlineStr"/>
-      <c r="AO76" t="inlineStr"/>
-      <c r="AP76" t="inlineStr"/>
-      <c r="AQ76" t="inlineStr"/>
-      <c r="AR76" t="inlineStr"/>
-      <c r="AS76" t="inlineStr"/>
-      <c r="AT76" t="inlineStr"/>
-      <c r="AU76" t="inlineStr"/>
-      <c r="AV76" t="inlineStr"/>
-      <c r="AW76" t="inlineStr"/>
-      <c r="AX76" t="inlineStr"/>
-      <c r="AY76" t="inlineStr"/>
-      <c r="AZ76" t="inlineStr"/>
-      <c r="BA76" t="inlineStr"/>
-      <c r="BB76" t="inlineStr"/>
-      <c r="BC76" t="inlineStr"/>
-      <c r="BD76" t="inlineStr"/>
-      <c r="BE76" t="inlineStr"/>
-      <c r="BF76" t="inlineStr"/>
-      <c r="BG76" t="inlineStr"/>
-      <c r="BH76" t="inlineStr"/>
-      <c r="BI76" t="inlineStr"/>
-      <c r="BJ76" t="inlineStr"/>
-      <c r="BK76" t="inlineStr"/>
-      <c r="BL76" t="inlineStr"/>
-      <c r="BM76" t="inlineStr"/>
-      <c r="BN76" t="inlineStr"/>
-      <c r="BO76" t="inlineStr"/>
-      <c r="BP76" t="inlineStr"/>
-      <c r="BQ76" t="inlineStr"/>
-      <c r="BR76" t="inlineStr"/>
-      <c r="BS76" t="inlineStr"/>
-      <c r="BT76" t="inlineStr"/>
-      <c r="BU76" t="inlineStr"/>
-      <c r="BV76" t="inlineStr"/>
-      <c r="BW76" t="inlineStr"/>
-      <c r="BX76" t="inlineStr"/>
-      <c r="BY76" t="inlineStr"/>
-      <c r="BZ76" t="inlineStr"/>
-      <c r="CA76" t="inlineStr"/>
-      <c r="CB76" t="inlineStr"/>
-      <c r="CC76" t="inlineStr"/>
-      <c r="CD76" t="inlineStr"/>
-      <c r="CE76" t="inlineStr"/>
-      <c r="CF76" t="inlineStr"/>
-      <c r="CG76" t="inlineStr"/>
-      <c r="CH76" t="inlineStr"/>
-      <c r="CI76" t="inlineStr"/>
-      <c r="CJ76" t="inlineStr"/>
-      <c r="CK76" t="inlineStr"/>
-      <c r="CL76" t="inlineStr"/>
-      <c r="CM76" t="inlineStr"/>
-      <c r="CN76" t="inlineStr"/>
-      <c r="CO76" t="inlineStr"/>
-      <c r="CP76" t="inlineStr"/>
-      <c r="CQ76" t="inlineStr"/>
-      <c r="CR76" t="inlineStr"/>
-      <c r="CS76" t="inlineStr"/>
-      <c r="CT76" t="inlineStr"/>
+        <v>0.1312694330000048</v>
+      </c>
+      <c r="AM76" t="n">
+        <v>0.241</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>-2.7467</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>-2.7071</v>
+      </c>
+      <c r="AP76" t="n">
+        <v>1.4729</v>
+      </c>
+      <c r="AQ76" t="n">
+        <v>-0.4656</v>
+      </c>
+      <c r="AR76" t="n">
+        <v>1.2599</v>
+      </c>
+      <c r="AS76" t="n">
+        <v>4.4786</v>
+      </c>
+      <c r="AT76" t="n">
+        <v>-0.0276</v>
+      </c>
+      <c r="AU76" t="n">
+        <v>4.4773</v>
+      </c>
+      <c r="AV76" t="n">
+        <v>0.1094</v>
+      </c>
+      <c r="AW76" t="n">
+        <v>-1.8612</v>
+      </c>
+      <c r="AX76" t="n">
+        <v>-1.8296</v>
+      </c>
+      <c r="AY76" t="n">
+        <v>0.8066</v>
+      </c>
+      <c r="AZ76" t="n">
+        <v>-3.6312</v>
+      </c>
+      <c r="BA76" t="n">
+        <v>-3.5412</v>
+      </c>
+      <c r="BB76" t="n">
+        <v>1.6473</v>
+      </c>
+      <c r="BC76" t="n">
+        <v>-3.4769</v>
+      </c>
+      <c r="BD76" t="n">
+        <v>-3.1702</v>
+      </c>
+      <c r="BE76" t="n">
+        <v>3.4595</v>
+      </c>
+      <c r="BF76" t="n">
+        <v>-2.1054</v>
+      </c>
+      <c r="BG76" t="n">
+        <v>2.9444</v>
+      </c>
+      <c r="BH76" t="n">
+        <v>5.7787</v>
+      </c>
+      <c r="BI76" t="n">
+        <v>-0.8456</v>
+      </c>
+      <c r="BJ76" t="n">
+        <v>5.7576</v>
+      </c>
+      <c r="BK76" t="n">
+        <v>3.4617</v>
+      </c>
+      <c r="BL76" t="n">
+        <v>-2.3829</v>
+      </c>
+      <c r="BM76" t="n">
+        <v>2.7659</v>
+      </c>
+      <c r="BN76" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="BO76" t="n">
+        <v>-2.6556</v>
+      </c>
+      <c r="BP76" t="n">
+        <v>-2.5873</v>
+      </c>
+      <c r="BQ76" t="n">
+        <v>0.1481</v>
+      </c>
+      <c r="BR76" t="n">
+        <v>-2.2037</v>
+      </c>
+      <c r="BS76" t="n">
+        <v>-2.1695</v>
+      </c>
+      <c r="BT76" t="n">
+        <v>1.2319</v>
+      </c>
+      <c r="BU76" t="n">
+        <v>-0.3652</v>
+      </c>
+      <c r="BV76" t="n">
+        <v>1.0431</v>
+      </c>
+      <c r="BW76" t="n">
+        <v>4.2603</v>
+      </c>
+      <c r="BX76" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="BY76" t="n">
+        <v>4.2595</v>
+      </c>
+      <c r="BZ76" t="n">
+        <v>0.1221</v>
+      </c>
+      <c r="CA76" t="n">
+        <v>-1.5255</v>
+      </c>
+      <c r="CB76" t="n">
+        <v>-1.4806</v>
+      </c>
+      <c r="CC76" t="n">
+        <v>0.5057</v>
+      </c>
+      <c r="CD76" t="n">
+        <v>-3.2505</v>
+      </c>
+      <c r="CE76" t="n">
+        <v>-3.1854</v>
+      </c>
+      <c r="CF76" t="n">
+        <v>1.2144</v>
+      </c>
+      <c r="CG76" t="n">
+        <v>-3.0737</v>
+      </c>
+      <c r="CH76" t="n">
+        <v>-2.8276</v>
+      </c>
+      <c r="CI76" t="n">
+        <v>2.9284</v>
+      </c>
+      <c r="CJ76" t="n">
+        <v>-1.8726</v>
+      </c>
+      <c r="CK76" t="n">
+        <v>2.3077</v>
+      </c>
+      <c r="CL76" t="n">
+        <v>5.3765</v>
+      </c>
+      <c r="CM76" t="n">
+        <v>-0.6819</v>
+      </c>
+      <c r="CN76" t="n">
+        <v>5.3554</v>
+      </c>
+      <c r="CO76" t="n">
+        <v>2.568</v>
+      </c>
+      <c r="CP76" t="n">
+        <v>-2.0174</v>
+      </c>
+      <c r="CQ76" t="n">
+        <v>1.5268</v>
+      </c>
+      <c r="CR76" t="n">
+        <v>0.2192</v>
+      </c>
+      <c r="CS76" t="n">
+        <v>-2.1385</v>
+      </c>
+      <c r="CT76" t="n">
+        <v>-2.0837</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
@@ -45385,13 +47950,13 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF77" t="n">
         <v>0</v>
       </c>
       <c r="AG77" s="6" t="n">
-        <v>0.75</v>
+        <v>0.7281553398058253</v>
       </c>
       <c r="AH77" s="6" t="n">
         <v>0.4188034188034188</v>
@@ -45400,74 +47965,194 @@
         <v>-0.4370477568740955</v>
       </c>
       <c r="AJ77" s="6" t="n">
-        <v>0.0002473960639255284</v>
+        <v>-0.005462221777095377</v>
       </c>
       <c r="AK77" s="6" t="n">
         <v>0.07403651115618662</v>
       </c>
       <c r="AL77" s="6" t="n">
-        <v>0.03714195361005607</v>
-      </c>
-      <c r="AM77" t="inlineStr"/>
-      <c r="AN77" t="inlineStr"/>
-      <c r="AO77" t="inlineStr"/>
-      <c r="AP77" t="inlineStr"/>
-      <c r="AQ77" t="inlineStr"/>
-      <c r="AR77" t="inlineStr"/>
-      <c r="AS77" t="inlineStr"/>
-      <c r="AT77" t="inlineStr"/>
-      <c r="AU77" t="inlineStr"/>
-      <c r="AV77" t="inlineStr"/>
-      <c r="AW77" t="inlineStr"/>
-      <c r="AX77" t="inlineStr"/>
-      <c r="AY77" t="inlineStr"/>
-      <c r="AZ77" t="inlineStr"/>
-      <c r="BA77" t="inlineStr"/>
-      <c r="BB77" t="inlineStr"/>
-      <c r="BC77" t="inlineStr"/>
-      <c r="BD77" t="inlineStr"/>
-      <c r="BE77" t="inlineStr"/>
-      <c r="BF77" t="inlineStr"/>
-      <c r="BG77" t="inlineStr"/>
-      <c r="BH77" t="inlineStr"/>
-      <c r="BI77" t="inlineStr"/>
-      <c r="BJ77" t="inlineStr"/>
-      <c r="BK77" t="inlineStr"/>
-      <c r="BL77" t="inlineStr"/>
-      <c r="BM77" t="inlineStr"/>
-      <c r="BN77" t="inlineStr"/>
-      <c r="BO77" t="inlineStr"/>
-      <c r="BP77" t="inlineStr"/>
-      <c r="BQ77" t="inlineStr"/>
-      <c r="BR77" t="inlineStr"/>
-      <c r="BS77" t="inlineStr"/>
-      <c r="BT77" t="inlineStr"/>
-      <c r="BU77" t="inlineStr"/>
-      <c r="BV77" t="inlineStr"/>
-      <c r="BW77" t="inlineStr"/>
-      <c r="BX77" t="inlineStr"/>
-      <c r="BY77" t="inlineStr"/>
-      <c r="BZ77" t="inlineStr"/>
-      <c r="CA77" t="inlineStr"/>
-      <c r="CB77" t="inlineStr"/>
-      <c r="CC77" t="inlineStr"/>
-      <c r="CD77" t="inlineStr"/>
-      <c r="CE77" t="inlineStr"/>
-      <c r="CF77" t="inlineStr"/>
-      <c r="CG77" t="inlineStr"/>
-      <c r="CH77" t="inlineStr"/>
-      <c r="CI77" t="inlineStr"/>
-      <c r="CJ77" t="inlineStr"/>
-      <c r="CK77" t="inlineStr"/>
-      <c r="CL77" t="inlineStr"/>
-      <c r="CM77" t="inlineStr"/>
-      <c r="CN77" t="inlineStr"/>
-      <c r="CO77" t="inlineStr"/>
-      <c r="CP77" t="inlineStr"/>
-      <c r="CQ77" t="inlineStr"/>
-      <c r="CR77" t="inlineStr"/>
-      <c r="CS77" t="inlineStr"/>
-      <c r="CT77" t="inlineStr"/>
+        <v>0.03428714468954562</v>
+      </c>
+      <c r="AM77" t="n">
+        <v>0.9449</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>-2.6028</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>-2.3645</v>
+      </c>
+      <c r="AP77" t="n">
+        <v>1.7853</v>
+      </c>
+      <c r="AQ77" t="n">
+        <v>-1.0946</v>
+      </c>
+      <c r="AR77" t="n">
+        <v>1.2088</v>
+      </c>
+      <c r="AS77" t="n">
+        <v>4.8797</v>
+      </c>
+      <c r="AT77" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU77" t="n">
+        <v>4.8797</v>
+      </c>
+      <c r="AV77" t="n">
+        <v>0.1785</v>
+      </c>
+      <c r="AW77" t="n">
+        <v>-3.0794</v>
+      </c>
+      <c r="AX77" t="n">
+        <v>-3.0567</v>
+      </c>
+      <c r="AY77" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="AZ77" t="n">
+        <v>-4.0889</v>
+      </c>
+      <c r="BA77" t="n">
+        <v>-4.0336</v>
+      </c>
+      <c r="BB77" t="n">
+        <v>1.8421</v>
+      </c>
+      <c r="BC77" t="n">
+        <v>-3.9955</v>
+      </c>
+      <c r="BD77" t="n">
+        <v>-3.7403</v>
+      </c>
+      <c r="BE77" t="n">
+        <v>2.2923</v>
+      </c>
+      <c r="BF77" t="n">
+        <v>-2.7722</v>
+      </c>
+      <c r="BG77" t="n">
+        <v>-1.5526</v>
+      </c>
+      <c r="BH77" t="n">
+        <v>4.3873</v>
+      </c>
+      <c r="BI77" t="n">
+        <v>-1.3651</v>
+      </c>
+      <c r="BJ77" t="n">
+        <v>4.2743</v>
+      </c>
+      <c r="BK77" t="n">
+        <v>3.1379</v>
+      </c>
+      <c r="BL77" t="n">
+        <v>-2.122</v>
+      </c>
+      <c r="BM77" t="n">
+        <v>2.4462</v>
+      </c>
+      <c r="BN77" t="n">
+        <v>0.9036999999999999</v>
+      </c>
+      <c r="BO77" t="n">
+        <v>-3.3832</v>
+      </c>
+      <c r="BP77" t="n">
+        <v>-3.2575</v>
+      </c>
+      <c r="BQ77" t="n">
+        <v>0.5467</v>
+      </c>
+      <c r="BR77" t="n">
+        <v>-2.1471</v>
+      </c>
+      <c r="BS77" t="n">
+        <v>-1.9887</v>
+      </c>
+      <c r="BT77" t="n">
+        <v>1.5722</v>
+      </c>
+      <c r="BU77" t="n">
+        <v>-0.9373</v>
+      </c>
+      <c r="BV77" t="n">
+        <v>1.0417</v>
+      </c>
+      <c r="BW77" t="n">
+        <v>4.6839</v>
+      </c>
+      <c r="BX77" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY77" t="n">
+        <v>4.6839</v>
+      </c>
+      <c r="BZ77" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="CA77" t="n">
+        <v>-2.6109</v>
+      </c>
+      <c r="CB77" t="n">
+        <v>-2.5842</v>
+      </c>
+      <c r="CC77" t="n">
+        <v>0.5379</v>
+      </c>
+      <c r="CD77" t="n">
+        <v>-3.6053</v>
+      </c>
+      <c r="CE77" t="n">
+        <v>-3.5507</v>
+      </c>
+      <c r="CF77" t="n">
+        <v>1.2956</v>
+      </c>
+      <c r="CG77" t="n">
+        <v>-3.597</v>
+      </c>
+      <c r="CH77" t="n">
+        <v>-3.4122</v>
+      </c>
+      <c r="CI77" t="n">
+        <v>1.6639</v>
+      </c>
+      <c r="CJ77" t="n">
+        <v>-2.4506</v>
+      </c>
+      <c r="CK77" t="n">
+        <v>-1.7214</v>
+      </c>
+      <c r="CL77" t="n">
+        <v>4.0783</v>
+      </c>
+      <c r="CM77" t="n">
+        <v>-1.0841</v>
+      </c>
+      <c r="CN77" t="n">
+        <v>3.9793</v>
+      </c>
+      <c r="CO77" t="n">
+        <v>2.2388</v>
+      </c>
+      <c r="CP77" t="n">
+        <v>-1.9702</v>
+      </c>
+      <c r="CQ77" t="n">
+        <v>0.8495</v>
+      </c>
+      <c r="CR77" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="CS77" t="n">
+        <v>-2.9943</v>
+      </c>
+      <c r="CT77" t="n">
+        <v>-2.9052</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
@@ -45557,13 +48242,13 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF78" t="n">
         <v>0</v>
       </c>
       <c r="AG78" s="6" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.6859504132231405</v>
       </c>
       <c r="AH78" s="6" t="n">
         <v>0.286624203821656</v>
@@ -45572,77 +48257,1365 @@
         <v>-0.262483994878361</v>
       </c>
       <c r="AJ78" s="6" t="n">
-        <v>0.09355609798026393</v>
+        <v>0.06691471004989276</v>
       </c>
       <c r="AK78" s="6" t="n">
         <v>0.1218498311249675</v>
       </c>
       <c r="AL78" s="6" t="n">
-        <v>0.1077029645526157</v>
-      </c>
-      <c r="AM78" t="inlineStr"/>
-      <c r="AN78" t="inlineStr"/>
-      <c r="AO78" t="inlineStr"/>
-      <c r="AP78" t="inlineStr"/>
-      <c r="AQ78" t="inlineStr"/>
-      <c r="AR78" t="inlineStr"/>
-      <c r="AS78" t="inlineStr"/>
-      <c r="AT78" t="inlineStr"/>
-      <c r="AU78" t="inlineStr"/>
-      <c r="AV78" t="inlineStr"/>
-      <c r="AW78" t="inlineStr"/>
-      <c r="AX78" t="inlineStr"/>
-      <c r="AY78" t="inlineStr"/>
-      <c r="AZ78" t="inlineStr"/>
-      <c r="BA78" t="inlineStr"/>
-      <c r="BB78" t="inlineStr"/>
-      <c r="BC78" t="inlineStr"/>
-      <c r="BD78" t="inlineStr"/>
-      <c r="BE78" t="inlineStr"/>
-      <c r="BF78" t="inlineStr"/>
-      <c r="BG78" t="inlineStr"/>
-      <c r="BH78" t="inlineStr"/>
-      <c r="BI78" t="inlineStr"/>
-      <c r="BJ78" t="inlineStr"/>
-      <c r="BK78" t="inlineStr"/>
-      <c r="BL78" t="inlineStr"/>
-      <c r="BM78" t="inlineStr"/>
-      <c r="BN78" t="inlineStr"/>
-      <c r="BO78" t="inlineStr"/>
-      <c r="BP78" t="inlineStr"/>
-      <c r="BQ78" t="inlineStr"/>
-      <c r="BR78" t="inlineStr"/>
-      <c r="BS78" t="inlineStr"/>
-      <c r="BT78" t="inlineStr"/>
-      <c r="BU78" t="inlineStr"/>
-      <c r="BV78" t="inlineStr"/>
-      <c r="BW78" t="inlineStr"/>
-      <c r="BX78" t="inlineStr"/>
-      <c r="BY78" t="inlineStr"/>
-      <c r="BZ78" t="inlineStr"/>
-      <c r="CA78" t="inlineStr"/>
-      <c r="CB78" t="inlineStr"/>
-      <c r="CC78" t="inlineStr"/>
-      <c r="CD78" t="inlineStr"/>
-      <c r="CE78" t="inlineStr"/>
-      <c r="CF78" t="inlineStr"/>
-      <c r="CG78" t="inlineStr"/>
-      <c r="CH78" t="inlineStr"/>
-      <c r="CI78" t="inlineStr"/>
-      <c r="CJ78" t="inlineStr"/>
-      <c r="CK78" t="inlineStr"/>
-      <c r="CL78" t="inlineStr"/>
-      <c r="CM78" t="inlineStr"/>
-      <c r="CN78" t="inlineStr"/>
-      <c r="CO78" t="inlineStr"/>
-      <c r="CP78" t="inlineStr"/>
-      <c r="CQ78" t="inlineStr"/>
-      <c r="CR78" t="inlineStr"/>
-      <c r="CS78" t="inlineStr"/>
-      <c r="CT78" t="inlineStr"/>
+        <v>0.09438227058743015</v>
+      </c>
+      <c r="AM78" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>-1.1166</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>-1.0856</v>
+      </c>
+      <c r="AP78" t="n">
+        <v>0.9129</v>
+      </c>
+      <c r="AQ78" t="n">
+        <v>-0.673</v>
+      </c>
+      <c r="AR78" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="AS78" t="n">
+        <v>4.2252</v>
+      </c>
+      <c r="AT78" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU78" t="n">
+        <v>4.2252</v>
+      </c>
+      <c r="AV78" t="n">
+        <v>0.2139</v>
+      </c>
+      <c r="AW78" t="n">
+        <v>-1.4711</v>
+      </c>
+      <c r="AX78" t="n">
+        <v>-1.3855</v>
+      </c>
+      <c r="AY78" t="n">
+        <v>1.4385</v>
+      </c>
+      <c r="AZ78" t="n">
+        <v>-3.6612</v>
+      </c>
+      <c r="BA78" t="n">
+        <v>-3.4517</v>
+      </c>
+      <c r="BB78" t="n">
+        <v>1.5104</v>
+      </c>
+      <c r="BC78" t="n">
+        <v>-3.5504</v>
+      </c>
+      <c r="BD78" t="n">
+        <v>-3.3027</v>
+      </c>
+      <c r="BE78" t="n">
+        <v>2.0997</v>
+      </c>
+      <c r="BF78" t="n">
+        <v>-1.8477</v>
+      </c>
+      <c r="BG78" t="n">
+        <v>0.7544</v>
+      </c>
+      <c r="BH78" t="n">
+        <v>3.6005</v>
+      </c>
+      <c r="BI78" t="n">
+        <v>-1.1864</v>
+      </c>
+      <c r="BJ78" t="n">
+        <v>3.4402</v>
+      </c>
+      <c r="BK78" t="n">
+        <v>3.0526</v>
+      </c>
+      <c r="BL78" t="n">
+        <v>-1.6657</v>
+      </c>
+      <c r="BM78" t="n">
+        <v>2.6146</v>
+      </c>
+      <c r="BN78" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BO78" t="n">
+        <v>-3.4428</v>
+      </c>
+      <c r="BP78" t="n">
+        <v>-3.4088</v>
+      </c>
+      <c r="BQ78" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="BR78" t="n">
+        <v>-0.7923</v>
+      </c>
+      <c r="BS78" t="n">
+        <v>-0.755</v>
+      </c>
+      <c r="BT78" t="n">
+        <v>0.7932</v>
+      </c>
+      <c r="BU78" t="n">
+        <v>-0.1965</v>
+      </c>
+      <c r="BV78" t="n">
+        <v>0.6663</v>
+      </c>
+      <c r="BW78" t="n">
+        <v>4.0466</v>
+      </c>
+      <c r="BX78" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY78" t="n">
+        <v>4.0466</v>
+      </c>
+      <c r="BZ78" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="CA78" t="n">
+        <v>-1.2722</v>
+      </c>
+      <c r="CB78" t="n">
+        <v>-1.1729</v>
+      </c>
+      <c r="CC78" t="n">
+        <v>1.0843</v>
+      </c>
+      <c r="CD78" t="n">
+        <v>-3.3314</v>
+      </c>
+      <c r="CE78" t="n">
+        <v>-3.1612</v>
+      </c>
+      <c r="CF78" t="n">
+        <v>1.0759</v>
+      </c>
+      <c r="CG78" t="n">
+        <v>-3.2138</v>
+      </c>
+      <c r="CH78" t="n">
+        <v>-3.0303</v>
+      </c>
+      <c r="CI78" t="n">
+        <v>1.1975</v>
+      </c>
+      <c r="CJ78" t="n">
+        <v>-1.6219</v>
+      </c>
+      <c r="CK78" t="n">
+        <v>-0.8354</v>
+      </c>
+      <c r="CL78" t="n">
+        <v>3.2917</v>
+      </c>
+      <c r="CM78" t="n">
+        <v>-0.9075</v>
+      </c>
+      <c r="CN78" t="n">
+        <v>3.1565</v>
+      </c>
+      <c r="CO78" t="n">
+        <v>2.2194</v>
+      </c>
+      <c r="CP78" t="n">
+        <v>-1.5656</v>
+      </c>
+      <c r="CQ78" t="n">
+        <v>1.4312</v>
+      </c>
+      <c r="CR78" t="n">
+        <v>0.1698</v>
+      </c>
+      <c r="CS78" t="n">
+        <v>-2.9059</v>
+      </c>
+      <c r="CT78" t="n">
+        <v>-2.8817</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2026-W15</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D79" t="n">
+        <v>15</v>
+      </c>
+      <c r="E79" t="n">
+        <v>202615</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr"/>
+      <c r="K79" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="4" t="inlineStr"/>
+      <c r="N79" s="4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O79" t="n">
+        <v>1</v>
+      </c>
+      <c r="P79" s="4" t="inlineStr"/>
+      <c r="Q79" s="4" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R79" t="n">
+        <v>1</v>
+      </c>
+      <c r="S79" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T79" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="U79" t="n">
+        <v>0</v>
+      </c>
+      <c r="V79" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="W79" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="X79" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="Z79" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="AA79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AC79" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AD79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="6" t="n">
+        <v>0.7864077669902912</v>
+      </c>
+      <c r="AH79" s="6" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+      <c r="AI79" s="6" t="n">
+        <v>-0.2191235059760956</v>
+      </c>
+      <c r="AJ79" s="6" t="n">
+        <v>0.110472470964671</v>
+      </c>
+      <c r="AK79" s="6" t="n">
+        <v>0.1378848728246319</v>
+      </c>
+      <c r="AL79" s="6" t="n">
+        <v>0.1241786718946514</v>
+      </c>
+      <c r="AM79" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>-2.9573</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>-2.905</v>
+      </c>
+      <c r="AP79" t="n">
+        <v>2.6321</v>
+      </c>
+      <c r="AQ79" t="n">
+        <v>-0.7219</v>
+      </c>
+      <c r="AR79" t="n">
+        <v>2.4725</v>
+      </c>
+      <c r="AS79" t="n">
+        <v>3.788</v>
+      </c>
+      <c r="AT79" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU79" t="n">
+        <v>3.788</v>
+      </c>
+      <c r="AV79" t="n">
+        <v>0.0362</v>
+      </c>
+      <c r="AW79" t="n">
+        <v>-2.5166</v>
+      </c>
+      <c r="AX79" t="n">
+        <v>-2.5102</v>
+      </c>
+      <c r="AY79" t="n">
+        <v>1.3749</v>
+      </c>
+      <c r="AZ79" t="n">
+        <v>-3.1085</v>
+      </c>
+      <c r="BA79" t="n">
+        <v>-2.8138</v>
+      </c>
+      <c r="BB79" t="n">
+        <v>1.1887</v>
+      </c>
+      <c r="BC79" t="n">
+        <v>-3.0673</v>
+      </c>
+      <c r="BD79" t="n">
+        <v>-2.8283</v>
+      </c>
+      <c r="BE79" t="n">
+        <v>2.1344</v>
+      </c>
+      <c r="BF79" t="n">
+        <v>-2.274</v>
+      </c>
+      <c r="BG79" t="n">
+        <v>-0.5322</v>
+      </c>
+      <c r="BH79" t="n">
+        <v>4.7339</v>
+      </c>
+      <c r="BI79" t="n">
+        <v>-1.3501</v>
+      </c>
+      <c r="BJ79" t="n">
+        <v>4.6474</v>
+      </c>
+      <c r="BK79" t="n">
+        <v>2.7632</v>
+      </c>
+      <c r="BL79" t="n">
+        <v>-2.0223</v>
+      </c>
+      <c r="BM79" t="n">
+        <v>1.8978</v>
+      </c>
+      <c r="BN79" t="n">
+        <v>1.8877</v>
+      </c>
+      <c r="BO79" t="n">
+        <v>-3.3528</v>
+      </c>
+      <c r="BP79" t="n">
+        <v>-2.9099</v>
+      </c>
+      <c r="BQ79" t="n">
+        <v>0.2222</v>
+      </c>
+      <c r="BR79" t="n">
+        <v>-2.4101</v>
+      </c>
+      <c r="BS79" t="n">
+        <v>-2.3642</v>
+      </c>
+      <c r="BT79" t="n">
+        <v>2.2569</v>
+      </c>
+      <c r="BU79" t="n">
+        <v>-0.5517</v>
+      </c>
+      <c r="BV79" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="BW79" t="n">
+        <v>3.6073</v>
+      </c>
+      <c r="BX79" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY79" t="n">
+        <v>3.6073</v>
+      </c>
+      <c r="BZ79" t="n">
+        <v>0.1035</v>
+      </c>
+      <c r="CA79" t="n">
+        <v>-2.0647</v>
+      </c>
+      <c r="CB79" t="n">
+        <v>-2.0389</v>
+      </c>
+      <c r="CC79" t="n">
+        <v>1.0379</v>
+      </c>
+      <c r="CD79" t="n">
+        <v>-2.7146</v>
+      </c>
+      <c r="CE79" t="n">
+        <v>-2.4623</v>
+      </c>
+      <c r="CF79" t="n">
+        <v>0.7416</v>
+      </c>
+      <c r="CG79" t="n">
+        <v>-2.7015</v>
+      </c>
+      <c r="CH79" t="n">
+        <v>-2.5442</v>
+      </c>
+      <c r="CI79" t="n">
+        <v>1.6183</v>
+      </c>
+      <c r="CJ79" t="n">
+        <v>-2.0861</v>
+      </c>
+      <c r="CK79" t="n">
+        <v>-1.1216</v>
+      </c>
+      <c r="CL79" t="n">
+        <v>4.3819</v>
+      </c>
+      <c r="CM79" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="CN79" t="n">
+        <v>4.2718</v>
+      </c>
+      <c r="CO79" t="n">
+        <v>1.9213</v>
+      </c>
+      <c r="CP79" t="n">
+        <v>-1.7273</v>
+      </c>
+      <c r="CQ79" t="n">
+        <v>0.5622</v>
+      </c>
+      <c r="CR79" t="n">
+        <v>1.4867</v>
+      </c>
+      <c r="CS79" t="n">
+        <v>-2.9556</v>
+      </c>
+      <c r="CT79" t="n">
+        <v>-2.5742</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2026-W16</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D80" t="n">
+        <v>16</v>
+      </c>
+      <c r="E80" t="n">
+        <v>202616</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr"/>
+      <c r="K80" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L80" t="n">
+        <v>1</v>
+      </c>
+      <c r="M80" s="4" t="inlineStr"/>
+      <c r="N80" s="4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1</v>
+      </c>
+      <c r="P80" s="4" t="inlineStr"/>
+      <c r="Q80" s="4" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1</v>
+      </c>
+      <c r="S80" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T80" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
+      </c>
+      <c r="V80" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="W80" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="X80" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="Z80" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB80" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AC80" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG80" s="6" t="n">
+        <v>0.6880733944954128</v>
+      </c>
+      <c r="AH80" s="6" t="n">
+        <v>0.2380952380952381</v>
+      </c>
+      <c r="AI80" s="6" t="n">
+        <v>-0.2512820512820513</v>
+      </c>
+      <c r="AJ80" s="6" t="n">
+        <v>0.06687791935569266</v>
+      </c>
+      <c r="AK80" s="6" t="n">
+        <v>0.07456</v>
+      </c>
+      <c r="AL80" s="6" t="n">
+        <v>0.07071895967784633</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>0.1836</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>-1.643</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>-1.5789</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>1.0221</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>-0.5624</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>0.6362</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>3.5082</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>3.5082</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>0.2708</v>
+      </c>
+      <c r="AW80" t="n">
+        <v>-2.0426</v>
+      </c>
+      <c r="AX80" t="n">
+        <v>-1.9685</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>0.9311</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>-4.1604</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>-4.0853</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>-3.9013</v>
+      </c>
+      <c r="BD80" t="n">
+        <v>-2.769</v>
+      </c>
+      <c r="BE80" t="n">
+        <v>2.6725</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>-3.173</v>
+      </c>
+      <c r="BG80" t="n">
+        <v>-1.8654</v>
+      </c>
+      <c r="BH80" t="n">
+        <v>4.3789</v>
+      </c>
+      <c r="BI80" t="n">
+        <v>-1.4892</v>
+      </c>
+      <c r="BJ80" t="n">
+        <v>4.2478</v>
+      </c>
+      <c r="BK80" t="n">
+        <v>1.6866</v>
+      </c>
+      <c r="BL80" t="n">
+        <v>-2.2104</v>
+      </c>
+      <c r="BM80" t="n">
+        <v>-1.2685</v>
+      </c>
+      <c r="BN80" t="n">
+        <v>0.5974</v>
+      </c>
+      <c r="BO80" t="n">
+        <v>-2.9463</v>
+      </c>
+      <c r="BP80" t="n">
+        <v>-2.8469</v>
+      </c>
+      <c r="BQ80" t="n">
+        <v>0.1292</v>
+      </c>
+      <c r="BR80" t="n">
+        <v>-1.2769</v>
+      </c>
+      <c r="BS80" t="n">
+        <v>-1.22</v>
+      </c>
+      <c r="BT80" t="n">
+        <v>0.9207</v>
+      </c>
+      <c r="BU80" t="n">
+        <v>-0.4438</v>
+      </c>
+      <c r="BV80" t="n">
+        <v>0.6162</v>
+      </c>
+      <c r="BW80" t="n">
+        <v>3.2982</v>
+      </c>
+      <c r="BX80" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY80" t="n">
+        <v>3.2982</v>
+      </c>
+      <c r="BZ80" t="n">
+        <v>0.1745</v>
+      </c>
+      <c r="CA80" t="n">
+        <v>-1.7085</v>
+      </c>
+      <c r="CB80" t="n">
+        <v>-1.6505</v>
+      </c>
+      <c r="CC80" t="n">
+        <v>0.6621</v>
+      </c>
+      <c r="CD80" t="n">
+        <v>-3.7621</v>
+      </c>
+      <c r="CE80" t="n">
+        <v>-3.6988</v>
+      </c>
+      <c r="CF80" t="n">
+        <v>2.2297</v>
+      </c>
+      <c r="CG80" t="n">
+        <v>-3.5366</v>
+      </c>
+      <c r="CH80" t="n">
+        <v>-2.9844</v>
+      </c>
+      <c r="CI80" t="n">
+        <v>2.056</v>
+      </c>
+      <c r="CJ80" t="n">
+        <v>-2.8608</v>
+      </c>
+      <c r="CK80" t="n">
+        <v>-2.0378</v>
+      </c>
+      <c r="CL80" t="n">
+        <v>4.0346</v>
+      </c>
+      <c r="CM80" t="n">
+        <v>-1.1268</v>
+      </c>
+      <c r="CN80" t="n">
+        <v>3.9264</v>
+      </c>
+      <c r="CO80" t="n">
+        <v>1.0546</v>
+      </c>
+      <c r="CP80" t="n">
+        <v>-2.0296</v>
+      </c>
+      <c r="CQ80" t="n">
+        <v>-1.5878</v>
+      </c>
+      <c r="CR80" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="CS80" t="n">
+        <v>-2.5093</v>
+      </c>
+      <c r="CT80" t="n">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-W17</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D81" t="n">
+        <v>17</v>
+      </c>
+      <c r="E81" t="n">
+        <v>202617</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="H81" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" t="n">
+        <v>1</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr"/>
+      <c r="K81" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L81" t="n">
+        <v>1</v>
+      </c>
+      <c r="M81" s="4" t="inlineStr"/>
+      <c r="N81" s="4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O81" t="n">
+        <v>1</v>
+      </c>
+      <c r="P81" s="4" t="inlineStr"/>
+      <c r="Q81" s="4" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R81" t="n">
+        <v>1</v>
+      </c>
+      <c r="S81" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T81" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="U81" t="n">
+        <v>0</v>
+      </c>
+      <c r="V81" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="W81" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="X81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="Z81" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="AA81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB81" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AC81" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF81" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG81" s="6" t="n">
+        <v>0.6883116883116883</v>
+      </c>
+      <c r="AH81" s="6" t="n">
+        <v>0.04035874439461883</v>
+      </c>
+      <c r="AI81" s="6" t="n">
+        <v>-0.2435703479576399</v>
+      </c>
+      <c r="AJ81" s="6" t="n">
+        <v>0.04214202741675304</v>
+      </c>
+      <c r="AK81" s="6" t="n">
+        <v>0.009624958513109858</v>
+      </c>
+      <c r="AL81" s="6" t="n">
+        <v>0.02588349296493145</v>
+      </c>
+      <c r="AM81" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>-2.2735</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>-2.1914</v>
+      </c>
+      <c r="AP81" t="n">
+        <v>1.0951</v>
+      </c>
+      <c r="AQ81" t="n">
+        <v>-0.5065</v>
+      </c>
+      <c r="AR81" t="n">
+        <v>0.7788</v>
+      </c>
+      <c r="AS81" t="n">
+        <v>3.6985</v>
+      </c>
+      <c r="AT81" t="n">
+        <v>-0.0638</v>
+      </c>
+      <c r="AU81" t="n">
+        <v>3.6934</v>
+      </c>
+      <c r="AV81" t="n">
+        <v>0.1255</v>
+      </c>
+      <c r="AW81" t="n">
+        <v>-1.559</v>
+      </c>
+      <c r="AX81" t="n">
+        <v>-1.5138</v>
+      </c>
+      <c r="AY81" t="n">
+        <v>0.6987</v>
+      </c>
+      <c r="AZ81" t="n">
+        <v>-4.2835</v>
+      </c>
+      <c r="BA81" t="n">
+        <v>-4.2366</v>
+      </c>
+      <c r="BB81" t="n">
+        <v>1.5467</v>
+      </c>
+      <c r="BC81" t="n">
+        <v>-4.1642</v>
+      </c>
+      <c r="BD81" t="n">
+        <v>-4.0006</v>
+      </c>
+      <c r="BE81" t="n">
+        <v>2.8576</v>
+      </c>
+      <c r="BF81" t="n">
+        <v>-3.3365</v>
+      </c>
+      <c r="BG81" t="n">
+        <v>-1.9461</v>
+      </c>
+      <c r="BH81" t="n">
+        <v>3.8601</v>
+      </c>
+      <c r="BI81" t="n">
+        <v>-1.6214</v>
+      </c>
+      <c r="BJ81" t="n">
+        <v>3.6375</v>
+      </c>
+      <c r="BK81" t="n">
+        <v>1.3895</v>
+      </c>
+      <c r="BL81" t="n">
+        <v>-1.6831</v>
+      </c>
+      <c r="BM81" t="n">
+        <v>-0.6701</v>
+      </c>
+      <c r="BN81" t="n">
+        <v>0.5049</v>
+      </c>
+      <c r="BO81" t="n">
+        <v>-3.1317</v>
+      </c>
+      <c r="BP81" t="n">
+        <v>-3.0611</v>
+      </c>
+      <c r="BQ81" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="BR81" t="n">
+        <v>-1.7612</v>
+      </c>
+      <c r="BS81" t="n">
+        <v>-1.6866</v>
+      </c>
+      <c r="BT81" t="n">
+        <v>1.0431</v>
+      </c>
+      <c r="BU81" t="n">
+        <v>-0.3913</v>
+      </c>
+      <c r="BV81" t="n">
+        <v>0.8066</v>
+      </c>
+      <c r="BW81" t="n">
+        <v>3.5401</v>
+      </c>
+      <c r="BX81" t="n">
+        <v>-0.0446</v>
+      </c>
+      <c r="BY81" t="n">
+        <v>3.5362</v>
+      </c>
+      <c r="BZ81" t="n">
+        <v>0.1184</v>
+      </c>
+      <c r="CA81" t="n">
+        <v>-1.2502</v>
+      </c>
+      <c r="CB81" t="n">
+        <v>-1.1974</v>
+      </c>
+      <c r="CC81" t="n">
+        <v>0.5132</v>
+      </c>
+      <c r="CD81" t="n">
+        <v>-3.8559</v>
+      </c>
+      <c r="CE81" t="n">
+        <v>-3.8127</v>
+      </c>
+      <c r="CF81" t="n">
+        <v>1.0664</v>
+      </c>
+      <c r="CG81" t="n">
+        <v>-3.8059</v>
+      </c>
+      <c r="CH81" t="n">
+        <v>-3.6884</v>
+      </c>
+      <c r="CI81" t="n">
+        <v>2.334</v>
+      </c>
+      <c r="CJ81" t="n">
+        <v>-3.017</v>
+      </c>
+      <c r="CK81" t="n">
+        <v>-2.0189</v>
+      </c>
+      <c r="CL81" t="n">
+        <v>3.5236</v>
+      </c>
+      <c r="CM81" t="n">
+        <v>-1.4236</v>
+      </c>
+      <c r="CN81" t="n">
+        <v>3.2954</v>
+      </c>
+      <c r="CO81" t="n">
+        <v>0.8035</v>
+      </c>
+      <c r="CP81" t="n">
+        <v>-1.4988</v>
+      </c>
+      <c r="CQ81" t="n">
+        <v>-1.0571</v>
+      </c>
+      <c r="CR81" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="CS81" t="n">
+        <v>-2.7813</v>
+      </c>
+      <c r="CT81" t="n">
+        <v>-2.7605</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-W18</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D82" t="n">
+        <v>18</v>
+      </c>
+      <c r="E82" t="n">
+        <v>202618</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>1</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr"/>
+      <c r="K82" s="4" t="n">
+        <v>52.7</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1</v>
+      </c>
+      <c r="M82" s="4" t="inlineStr"/>
+      <c r="N82" s="4" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1</v>
+      </c>
+      <c r="P82" s="4" t="inlineStr"/>
+      <c r="Q82" s="4" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1</v>
+      </c>
+      <c r="S82" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="T82" s="5" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="U82" t="n">
+        <v>0</v>
+      </c>
+      <c r="V82" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="W82" s="4" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="X82" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="Z82" s="3" t="n">
+        <v>60.25608211228174</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB82" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AC82" s="3" t="n">
+        <v>52.69722222222222</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG82" s="6" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AH82" s="6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AI82" s="6" t="n">
+        <v>-0.1587301587301587</v>
+      </c>
+      <c r="AJ82" s="6" t="n">
+        <v>0.0732244276596991</v>
+      </c>
+      <c r="AK82" s="6" t="n">
+        <v>0.1154303847679492</v>
+      </c>
+      <c r="AL82" s="6" t="n">
+        <v>0.09432740621382416</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>0.0551</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>-1.2732</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>-1.2498</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>1.9865</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>-0.369</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>1.8763</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>3.0365</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>-0.2399</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>3.0043</v>
+      </c>
+      <c r="AV82" t="n">
+        <v>0.0534</v>
+      </c>
+      <c r="AW82" t="n">
+        <v>-2.0539</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>-2.0407</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>1.1117</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>-4.0548</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>-3.9503</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>1.6203</v>
+      </c>
+      <c r="BC82" t="n">
+        <v>-3.8672</v>
+      </c>
+      <c r="BD82" t="n">
+        <v>-3.646</v>
+      </c>
+      <c r="BE82" t="n">
+        <v>2.6413</v>
+      </c>
+      <c r="BF82" t="n">
+        <v>-3.7155</v>
+      </c>
+      <c r="BG82" t="n">
+        <v>-2.9814</v>
+      </c>
+      <c r="BH82" t="n">
+        <v>3.7522</v>
+      </c>
+      <c r="BI82" t="n">
+        <v>-1.6236</v>
+      </c>
+      <c r="BJ82" t="n">
+        <v>3.5101</v>
+      </c>
+      <c r="BK82" t="n">
+        <v>1.4559</v>
+      </c>
+      <c r="BL82" t="n">
+        <v>-1.6614</v>
+      </c>
+      <c r="BM82" t="n">
+        <v>-0.506</v>
+      </c>
+      <c r="BN82" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="BO82" t="n">
+        <v>-2.6749</v>
+      </c>
+      <c r="BP82" t="n">
+        <v>-2.636</v>
+      </c>
+      <c r="BQ82" t="n">
+        <v>0.0403</v>
+      </c>
+      <c r="BR82" t="n">
+        <v>-0.9604</v>
+      </c>
+      <c r="BS82" t="n">
+        <v>-0.9393</v>
+      </c>
+      <c r="BT82" t="n">
+        <v>1.8382</v>
+      </c>
+      <c r="BU82" t="n">
+        <v>-0.3019</v>
+      </c>
+      <c r="BV82" t="n">
+        <v>1.7411</v>
+      </c>
+      <c r="BW82" t="n">
+        <v>2.8293</v>
+      </c>
+      <c r="BX82" t="n">
+        <v>-0.2311</v>
+      </c>
+      <c r="BY82" t="n">
+        <v>2.7936</v>
+      </c>
+      <c r="BZ82" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="CA82" t="n">
+        <v>-1.7219</v>
+      </c>
+      <c r="CB82" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="CC82" t="n">
+        <v>0.9461000000000001</v>
+      </c>
+      <c r="CD82" t="n">
+        <v>-3.6083</v>
+      </c>
+      <c r="CE82" t="n">
+        <v>-3.4942</v>
+      </c>
+      <c r="CF82" t="n">
+        <v>1.0596</v>
+      </c>
+      <c r="CG82" t="n">
+        <v>-3.4815</v>
+      </c>
+      <c r="CH82" t="n">
+        <v>-3.3342</v>
+      </c>
+      <c r="CI82" t="n">
+        <v>2.0325</v>
+      </c>
+      <c r="CJ82" t="n">
+        <v>-3.4029</v>
+      </c>
+      <c r="CK82" t="n">
+        <v>-2.9042</v>
+      </c>
+      <c r="CL82" t="n">
+        <v>3.427</v>
+      </c>
+      <c r="CM82" t="n">
+        <v>-1.3787</v>
+      </c>
+      <c r="CN82" t="n">
+        <v>3.1946</v>
+      </c>
+      <c r="CO82" t="n">
+        <v>0.9693000000000001</v>
+      </c>
+      <c r="CP82" t="n">
+        <v>-1.4281</v>
+      </c>
+      <c r="CQ82" t="n">
+        <v>-0.7934</v>
+      </c>
+      <c r="CR82" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="CS82" t="n">
+        <v>-2.3866</v>
+      </c>
+      <c r="CT82" t="n">
+        <v>-2.3679</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CT78"/>
+  <autoFilter ref="A1:CT82"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45763,7 +49736,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10">
@@ -45773,7 +49746,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11">
